--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Last refreshed: 2026-10-25</t>
+          <t>Last refreshed: 2026-10-26</t>
         </is>
       </c>
     </row>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Last refreshed: 2026-10-26</t>
+          <t>Last refreshed: 2026-10-27</t>
         </is>
       </c>
     </row>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Last refreshed: 2026-10-27</t>
+          <t>Last refreshed: 2026-10-28</t>
         </is>
       </c>
     </row>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$O$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -62,11 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -455,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,8 +558,587 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Patient Financial Advocacy Coordinator</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Onco360</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Louisville, Jefferson County</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>$45,760-$45,760</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2d4b990c73ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Youth Field Organizer (Remote in Oklahoma)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>The Company Rescue</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Enid, Garfield County</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>$44,000-$44,000</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>30f3c62085ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Digital Leadership Development Program Associate (July 2027 Start)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>GE Appliances</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Louisville, Jefferson County</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>$57,892-$57,892</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>e4ca2b2ba60f</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Influencer Outreach Coordinator</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Louisville, Jefferson County</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>$35,360-$49,920</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>faed5e64a495</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Social Media &amp; Digital Content Specialist</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>GE Appliances</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Louisville, Jefferson County</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>$76,219-$76,219</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>6e8cef3bfdea</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Graphic Designer &amp; Communications Coordinator - Remote Wisconsin</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Gainwell Technologies LLC</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>$68,402-$68,402</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>6d53bdabd788</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Digital Content Producer</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Louisville Metro Government</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Louisville, Jefferson County</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>$53,726-$53,726</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>67eb5ce931cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Family Engagement Specialist - Head Start/Early Head Start</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Family &amp; Children's Place</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Louisville, Jefferson County</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>$45,760-$47,840</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>14064eb9cf0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>FWS - Landowner and Farmer Outreach Organizer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Post University</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Waterbury, New Haven County</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>$41,600-$41,600</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Open posting</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>db5c8dc97894</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:O10"/>
   <conditionalFormatting sqref="A2:O2000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>OR($B2="Pass",$B2="Rejected")</formula>
@@ -570,6 +1155,17 @@
       <formula1>"New,Interested,Applied,Interview,Offer,Rejected,Pass"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -582,7 +582,7 @@
           <t>Louisville, Jefferson County</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>$45,760-$45,760</t>
@@ -712,7 +712,7 @@
           <t>Louisville, Jefferson County</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>$57,892-$57,892</t>
@@ -775,7 +775,7 @@
           <t>Louisville, Jefferson County</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>$35,360-$49,920</t>
@@ -838,7 +838,7 @@
           <t>Louisville, Jefferson County</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>$76,219-$76,219</t>
@@ -968,7 +968,7 @@
           <t>Louisville, Jefferson County</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>$53,726-$53,726</t>
@@ -1031,7 +1031,7 @@
           <t>Louisville, Jefferson County</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>$45,760-$47,840</t>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1213,7 +1213,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Last refreshed: 2026-10-28</t>
+          <t>Last refreshed: 2026-10-29</t>
         </is>
       </c>
     </row>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1213,7 +1213,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Last refreshed: 2026-10-29</t>
+          <t>Last refreshed: 2026-10-30</t>
         </is>
       </c>
     </row>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1213,7 +1213,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Last refreshed: 2026-10-30</t>
+          <t>Last refreshed: 2026-10-31</t>
         </is>
       </c>
     </row>
